--- a/8-School.mangement.system.ipyub/courses.xlsx
+++ b/8-School.mangement.system.ipyub/courses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,41 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ahmed Ali</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eng</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>Ahmed Khan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AL;I</t>
         </is>
       </c>
     </row>
